--- a/outputs/reports/gradient_boosting/feature_importance_top10.xlsx
+++ b/outputs/reports/gradient_boosting/feature_importance_top10.xlsx
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3551872132603224</v>
+        <v>0.2989836767503042</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09156760468956948</v>
+        <v>0.06737871042955795</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=35.52%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=29.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -515,10 +515,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1210067866128246</v>
+        <v>0.1900691609165165</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03119566580004468</v>
+        <v>0.04283382656264023</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=12.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=19.01%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.09550941880378003</v>
+        <v>0.1094318299389545</v>
       </c>
       <c r="F4" t="n">
-        <v>0.024622419891972</v>
+        <v>0.02466146533943159</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=9.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=10.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.08317300577179218</v>
+        <v>0.09961877929788324</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02144208076480753</v>
+        <v>0.02245000448390294</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=8.32%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=9.96%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0470834478530202</v>
+        <v>0.0671473708505427</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01213815807402807</v>
+        <v>0.01513227513227527</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04409184126514275</v>
+        <v>0.04746555881861263</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01136691902262477</v>
+        <v>0.01069679849340871</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04333072580815647</v>
+        <v>0.03771617760586961</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01117070272686144</v>
+        <v>0.008499686126804851</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.33%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.77%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03891202773842957</v>
+        <v>0.03252711919712811</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01003155812090184</v>
+        <v>0.007330284279436938</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.89%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=3.25%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03607898687075828</v>
+        <v>0.01931571281904346</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009301197464449407</v>
+        <v>0.004352972827549206</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=3.61%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=1.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.01897503118459181</v>
+        <v>0.01564676201163554</v>
       </c>
       <c r="F11" t="n">
-        <v>0.004891781262433892</v>
+        <v>0.003526141153259887</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=1.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=1.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
